--- a/data/trans_dic/IP25-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,15 +519,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que ven la televisión todos o casi todos los días</t>
+          <t>Menores que ven la televisión todos o casi todos los días (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -537,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -575,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -631,9 +611,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -663,47 +640,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>92,16%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>90,48%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -716,62 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,42; 94,33</t>
+          <t>86,3; 94,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,01; 95,76</t>
+          <t>88,95; 95,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,46; 92,97</t>
+          <t>84,39; 93,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>84,29; 92,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,86; 92,54</t>
+          <t>86,97; 94,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,58; 94,97</t>
+          <t>86,47; 94,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,74; 94,71</t>
+          <t>86,9; 92,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>89,27; 94,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>86,8; 92,49</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>89,19; 94,58</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>87,12; 93,35</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,52</t>
+          <t>87,3; 93,34</t>
         </is>
       </c>
     </row>
@@ -803,47 +750,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>90,53%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
           <t>90,8%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -856,62 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,38; 91,77</t>
+          <t>84,51; 91,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,15; 93,4</t>
+          <t>87,21; 93,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,13; 93,17</t>
+          <t>86,99; 93,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>83,26; 90,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,69; 90,03</t>
+          <t>86,98; 93,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,54; 93,37</t>
+          <t>87,78; 93,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,6; 93,74</t>
+          <t>84,61; 89,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>87,74; 92,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84,65; 89,97</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>87,81; 92,52</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>88,69; 92,82</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,31</t>
+          <t>88,46; 92,87</t>
         </is>
       </c>
     </row>
@@ -943,47 +860,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>87,61%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>94,14%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -996,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,96; 92,33</t>
+          <t>84,47; 92,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,67; 88,8</t>
+          <t>79,09; 88,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,97; 95,92</t>
+          <t>89,91; 95,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,84</t>
+          <t>83,44; 91,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,42; 91,97</t>
+          <t>86,36; 93,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,08; 93,59</t>
+          <t>91,54; 97,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,49; 97,14</t>
+          <t>85,3; 91,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>84,33; 90,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85,41; 91,14</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>84,44; 90,42</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>91,74; 95,86</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,42</t>
+          <t>91,76; 95,98</t>
         </is>
       </c>
     </row>
@@ -1083,47 +970,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>90,47%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>87,7%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,15; 95,29</t>
+          <t>89,3; 95,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,83; 91,82</t>
+          <t>84,55; 91,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,91; 90,45</t>
+          <t>82,5; 90,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>81,98; 89,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,24; 90,19</t>
+          <t>89,17; 95,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,93; 94,98</t>
+          <t>84,54; 91,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,32; 91,48</t>
+          <t>87,07; 92,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>87,99; 92,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,01; 91,87</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>87,79; 92,69</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>84,99; 90,24</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,4</t>
+          <t>84,84; 90,21</t>
         </is>
       </c>
     </row>
@@ -1223,47 +1080,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>90,2%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
           <t>90,6%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,22; 91,98</t>
+          <t>88,45; 92,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,15; 90,9</t>
+          <t>86,93; 90,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,05; 91,54</t>
+          <t>87,75; 91,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>85,37; 89,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>85,44; 89,42</t>
+          <t>89,6; 92,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,46; 92,82</t>
+          <t>89,47; 92,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,59; 92,99</t>
+          <t>87,52; 90,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>88,95; 91,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,56; 90,14</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>88,85; 91,43</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>89,26; 91,8</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,1</t>
+          <t>89,15; 91,76</t>
         </is>
       </c>
     </row>
@@ -1344,15 +1171,966 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que ven la televisión todos o casi todos los días (tasa de respuesta: 99,89%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>125497</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>128373</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>119665</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>136424</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>141750</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>135299</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>261921</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>270122</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>254964</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>119084; 129972</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>123120; 132779</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112834; 124683</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>129024; 142291</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>134522; 146591</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>128046; 140358</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>252945; 269216</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>261656; 277590</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>245999; 263013</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>172493</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>186935</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>187170</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>184092</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>201338</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>204716</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>356585</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>388273</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>391886</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>164940; 179257</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>179956; 192781</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>180287; 193346</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>176621; 191442</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>193573; 207823</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>196939; 210659</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>344613; 366275</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>376329; 396915</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>381812; 400834</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>122306</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>131328</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>145535</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>132113</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>149890</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>158233</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>254419</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>281218</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>303768</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>116416; 127228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>122883; 137865</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>140260; 149391</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>124876; 137519</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>143025; 155598</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>152571; 161821</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>245222; 261599</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>270675; 289790</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>296083; 309687</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>193455</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>186246</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>180363</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>179999</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>191873</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>181965</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>373454</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>378119</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>362327</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>186281; 198566</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177803; 193027</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>171116; 187404</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170377; 186912</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>185155; 197289</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>173919; 188295</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>362594; 383636</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>367757; 388251</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>350533; 372701</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1866</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>613750</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>632881</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>632732</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>632629</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>684852</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>680214</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1246379</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1317733</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1312946</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>601092; 625225</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>617612; 645912</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>618103; 644853</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>616993; 645702</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>672442; 697686</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>666379; 691435</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1227233; 1264402</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1299481; 1335811</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1292026; 1329840</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_dic/IP25-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,3; 94,19</t>
+          <t>86,63; 94,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,95; 95,93</t>
+          <t>88,41; 96,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,39; 93,25</t>
+          <t>84,64; 93,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,29; 92,95</t>
+          <t>84,42; 92,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,97; 94,77</t>
+          <t>87,8; 94,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,47; 94,79</t>
+          <t>86,55; 94,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,9; 92,49</t>
+          <t>87,0; 92,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>89,27; 94,71</t>
+          <t>88,88; 94,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,3; 93,34</t>
+          <t>87,24; 92,98</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,51; 91,85</t>
+          <t>84,27; 91,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,21; 93,42</t>
+          <t>87,0; 93,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,99; 93,29</t>
+          <t>87,04; 92,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83,26; 90,24</t>
+          <t>82,08; 90,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,98; 93,39</t>
+          <t>86,5; 93,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,78; 93,89</t>
+          <t>87,48; 93,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,61; 89,93</t>
+          <t>84,48; 89,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,74; 92,54</t>
+          <t>87,93; 92,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,46; 92,87</t>
+          <t>88,33; 92,66</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,47; 92,32</t>
+          <t>84,33; 92,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,09; 88,73</t>
+          <t>79,55; 88,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,91; 95,77</t>
+          <t>89,66; 95,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,44; 91,89</t>
+          <t>83,29; 91,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,36; 93,96</t>
+          <t>86,58; 93,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,54; 97,09</t>
+          <t>91,23; 97,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,3; 91,0</t>
+          <t>85,08; 91,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84,33; 90,28</t>
+          <t>84,52; 90,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91,76; 95,98</t>
+          <t>92,06; 96,04</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,3; 95,19</t>
+          <t>89,35; 95,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,55; 91,79</t>
+          <t>84,82; 92,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,5; 90,35</t>
+          <t>82,87; 90,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81,98; 89,94</t>
+          <t>82,17; 89,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,17; 95,01</t>
+          <t>88,36; 94,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,54; 91,52</t>
+          <t>84,11; 91,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,07; 92,13</t>
+          <t>87,05; 91,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87,99; 92,89</t>
+          <t>87,78; 92,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84,84; 90,21</t>
+          <t>84,87; 90,05</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,45; 92,0</t>
+          <t>88,33; 91,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,93; 90,92</t>
+          <t>87,07; 91,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,75; 91,55</t>
+          <t>87,83; 91,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,37; 89,35</t>
+          <t>85,31; 89,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>89,6; 92,97</t>
+          <t>89,36; 92,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,47; 92,83</t>
+          <t>89,44; 92,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,52; 90,17</t>
+          <t>87,53; 90,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88,95; 91,44</t>
+          <t>88,91; 91,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89,15; 91,76</t>
+          <t>89,31; 91,78</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>119084; 129972</t>
+          <t>119539; 130210</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>123120; 132779</t>
+          <t>122370; 132910</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112834; 124683</t>
+          <t>113169; 124626</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129024; 142291</t>
+          <t>129232; 141731</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>134522; 146591</t>
+          <t>135816; 146802</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>128046; 140358</t>
+          <t>128162; 140342</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>252945; 269216</t>
+          <t>253222; 269599</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>261656; 277590</t>
+          <t>260517; 276815</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>245999; 263013</t>
+          <t>245820; 261995</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>164940; 179257</t>
+          <t>164458; 178850</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>179956; 192781</t>
+          <t>179527; 192390</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>180287; 193346</t>
+          <t>180380; 192711</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>176621; 191442</t>
+          <t>174118; 191305</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>193573; 207823</t>
+          <t>192493; 207603</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>196939; 210659</t>
+          <t>196274; 210480</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>344613; 366275</t>
+          <t>344103; 365772</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>376329; 396915</t>
+          <t>377132; 397167</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381812; 400834</t>
+          <t>381241; 399924</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>116416; 127228</t>
+          <t>116227; 127562</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>122883; 137865</t>
+          <t>123595; 137958</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140260; 149391</t>
+          <t>139873; 149548</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124876; 137519</t>
+          <t>124654; 137625</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>143025; 155598</t>
+          <t>143380; 155503</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>152571; 161821</t>
+          <t>152064; 161949</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>245222; 261599</t>
+          <t>244577; 261746</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>270675; 289790</t>
+          <t>271293; 289547</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>296083; 309687</t>
+          <t>297059; 309879</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>186281; 198566</t>
+          <t>186389; 198997</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>177803; 193027</t>
+          <t>178378; 193619</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>171116; 187404</t>
+          <t>171884; 188163</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>170377; 186912</t>
+          <t>170765; 187003</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>185155; 197289</t>
+          <t>183475; 197006</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>173919; 188295</t>
+          <t>173048; 188385</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>362594; 383636</t>
+          <t>362518; 382593</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>367757; 388251</t>
+          <t>366870; 387420</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>350533; 372701</t>
+          <t>350627; 372030</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>601092; 625225</t>
+          <t>600298; 625132</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>617612; 645912</t>
+          <t>618615; 646696</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>618103; 644853</t>
+          <t>618652; 644628</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>616993; 645702</t>
+          <t>616543; 645662</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>672442; 697686</t>
+          <t>670650; 697623</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>666379; 691435</t>
+          <t>666188; 691607</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1227233; 1264402</t>
+          <t>1227346; 1263383</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1299481; 1335811</t>
+          <t>1298862; 1337184</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1292026; 1329840</t>
+          <t>1294340; 1330065</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP25-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89,12%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>91,64%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>91,37%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>90,94%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>92,74%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>89,5%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>89,12%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>91,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,63; 94,36</t>
+          <t>83,86; 92,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,41; 96,02</t>
+          <t>87,58; 94,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,64; 93,21</t>
+          <t>86,74; 94,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,42; 92,59</t>
+          <t>86,42; 94,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,8; 94,9</t>
+          <t>88,01; 95,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,55; 94,78</t>
+          <t>84,46; 92,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,0; 92,62</t>
+          <t>86,8; 92,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,88; 94,44</t>
+          <t>89,19; 94,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,24; 92,98</t>
+          <t>87,12; 93,35</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>86,78%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>90,47%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>91,24%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>88,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>90,59%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>90,31%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>86,78%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>90,47%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>91,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,27; 91,64</t>
+          <t>82,69; 90,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,0; 93,23</t>
+          <t>86,54; 93,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,04; 92,99</t>
+          <t>87,6; 93,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,08; 90,18</t>
+          <t>84,38; 91,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,5; 93,29</t>
+          <t>87,15; 93,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,48; 93,81</t>
+          <t>87,13; 93,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,48; 89,8</t>
+          <t>84,65; 89,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,93; 92,6</t>
+          <t>87,81; 92,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,33; 92,66</t>
+          <t>88,69; 92,82</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>88,28%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>90,51%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>88,75%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>84,52%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>93,29%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>90,51%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,33; 92,56</t>
+          <t>83,42; 91,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,55; 88,79</t>
+          <t>86,08; 93,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,66; 95,87</t>
+          <t>91,49; 97,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,29; 91,96</t>
+          <t>83,96; 92,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,58; 93,9</t>
+          <t>79,67; 88,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,23; 97,17</t>
+          <t>89,97; 95,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,08; 91,05</t>
+          <t>85,41; 91,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84,52; 90,21</t>
+          <t>84,44; 90,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92,06; 96,04</t>
+          <t>91,74; 95,86</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>86,61%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>92,4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>88,45%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>92,74%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>88,56%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>86,96%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>86,61%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>92,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>88,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,35; 95,39</t>
+          <t>82,24; 90,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,82; 92,07</t>
+          <t>88,93; 94,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,87; 90,72</t>
+          <t>84,32; 91,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82,17; 89,98</t>
+          <t>89,15; 95,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,36; 94,87</t>
+          <t>83,83; 91,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,11; 91,57</t>
+          <t>82,91; 90,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,05; 91,87</t>
+          <t>87,01; 91,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87,78; 92,7</t>
+          <t>87,79; 92,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84,87; 90,05</t>
+          <t>84,99; 90,24</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>87,54%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>91,25%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>90,31%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>89,08%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>89,83%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>87,54%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,33; 91,99</t>
+          <t>85,44; 89,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,07; 91,03</t>
+          <t>89,46; 92,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,83; 91,52</t>
+          <t>89,59; 92,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,31; 89,34</t>
+          <t>88,22; 91,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>89,36; 92,96</t>
+          <t>87,15; 90,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,44; 92,85</t>
+          <t>88,05; 91,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,53; 90,1</t>
+          <t>87,56; 90,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88,91; 91,53</t>
+          <t>88,85; 91,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89,31; 91,78</t>
+          <t>89,26; 91,8</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>166</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>136424</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>141750</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>135299</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>125497</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>128373</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>119665</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>136424</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>141750</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>135299</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>119539; 130210</t>
+          <t>128369; 141658</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>122370; 132910</t>
+          <t>135470; 146899</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113169; 124626</t>
+          <t>128440; 140246</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129232; 141731</t>
+          <t>119256; 130175</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>135816; 146802</t>
+          <t>121814; 132551</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>128162; 140342</t>
+          <t>112935; 124302</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>253222; 269599</t>
+          <t>252636; 269216</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>260517; 276815</t>
+          <t>261417; 277220</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>245820; 261995</t>
+          <t>245478; 263038</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>299</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>184092</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>201338</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>204716</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>172493</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>186935</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>187170</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>184092</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>201338</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>204716</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>164458; 178850</t>
+          <t>175429; 190993</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>179527; 192390</t>
+          <t>192576; 207792</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>180380; 192711</t>
+          <t>196540; 210317</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>174118; 191305</t>
+          <t>164679; 179097</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>192493; 207603</t>
+          <t>179832; 192748</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>196274; 210480</t>
+          <t>180580; 193083</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>344103; 365772</t>
+          <t>344767; 366467</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>377132; 397167</t>
+          <t>376606; 396832</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381241; 399924</t>
+          <t>382813; 400616</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>240</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>132113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>158233</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>122306</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>131328</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>145535</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>132113</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>149890</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>158233</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>116227; 127562</t>
+          <t>124842; 137640</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>123595; 137958</t>
+          <t>142551; 154985</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139873; 149548</t>
+          <t>152487; 161906</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124654; 137625</t>
+          <t>115713; 127253</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>143380; 155503</t>
+          <t>123795; 137980</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>152064; 161949</t>
+          <t>140347; 149634</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>244577; 261746</t>
+          <t>245542; 262017</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>271293; 289547</t>
+          <t>271044; 290232</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>297059; 309879</t>
+          <t>296024; 309315</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>242</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>243</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>179999</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>191873</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>181965</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>193455</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>186246</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>180363</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>179999</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>191873</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>181965</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>186389; 198997</t>
+          <t>170921; 187442</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>178378; 193619</t>
+          <t>184667; 197226</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>171884; 188163</t>
+          <t>173472; 188216</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>170765; 187003</t>
+          <t>185967; 198785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>183475; 197006</t>
+          <t>176300; 193091</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>173048; 188385</t>
+          <t>171963; 187613</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>362518; 382593</t>
+          <t>362331; 382585</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>366870; 387420</t>
+          <t>366922; 387387</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>350627; 372030</t>
+          <t>351154; 372821</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>909</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>948</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>978</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>971</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>632629</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>684852</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>680214</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>613750</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>632881</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>632732</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>632629</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>684852</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>680214</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>600298; 625132</t>
+          <t>617477; 646203</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>618615; 646696</t>
+          <t>671348; 696627</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>618652; 644628</t>
+          <t>667283; 692635</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>616543; 645662</t>
+          <t>599517; 625109</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>670650; 697623</t>
+          <t>619167; 645775</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>666188; 691607</t>
+          <t>620191; 644772</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1227346; 1263383</t>
+          <t>1227893; 1264024</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1298862; 1337184</t>
+          <t>1298087; 1335683</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1294340; 1330065</t>
+          <t>1293630; 1330342</t>
         </is>
       </c>
     </row>
